--- a/internal_doc/05.测试设计/自动化/SDV1自动化测试用例分类.xlsx
+++ b/internal_doc/05.测试设计/自动化/SDV1自动化测试用例分类.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="61">
   <si>
     <t>story</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -379,6 +379,10 @@
   </si>
   <si>
     <t>安排计划：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>龙阳</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -589,14 +593,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -978,8 +982,8 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="21"/>
-      <c r="D1" s="20" t="s">
+      <c r="C1" s="19"/>
+      <c r="D1" s="18" t="s">
         <v>49</v>
       </c>
       <c r="E1" s="9" t="s">
@@ -996,7 +1000,7 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="20" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1020,7 +1024,7 @@
       <c r="H2" s="16"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="19"/>
+      <c r="A3" s="21"/>
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1031,7 +1035,7 @@
         <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>36</v>
@@ -1044,7 +1048,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="22.5" customHeight="1">
-      <c r="A4" s="19"/>
+      <c r="A4" s="21"/>
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
@@ -1068,7 +1072,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="36" customHeight="1">
-      <c r="A5" s="19"/>
+      <c r="A5" s="21"/>
       <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
@@ -1089,7 +1093,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="13.5" hidden="1" customHeight="1">
-      <c r="A6" s="19"/>
+      <c r="A6" s="21"/>
       <c r="B6" s="5" t="s">
         <v>18</v>
       </c>
@@ -1111,7 +1115,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="13.5" hidden="1" customHeight="1">
-      <c r="A7" s="19"/>
+      <c r="A7" s="21"/>
       <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
@@ -1130,7 +1134,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="25.5" customHeight="1">
-      <c r="A8" s="19"/>
+      <c r="A8" s="21"/>
       <c r="B8" s="2" t="s">
         <v>41</v>
       </c>
@@ -1144,7 +1148,7 @@
         <v>45</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>29</v>
@@ -1154,7 +1158,7 @@
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="19"/>
+      <c r="A9" s="21"/>
       <c r="B9" s="2" t="s">
         <v>9</v>
       </c>
@@ -1176,7 +1180,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" hidden="1">
-      <c r="A10" s="19"/>
+      <c r="A10" s="21"/>
       <c r="B10" s="2" t="s">
         <v>10</v>
       </c>
@@ -1194,7 +1198,7 @@
       <c r="H10" s="16"/>
     </row>
     <row r="11" spans="1:8" ht="13.5" hidden="1" customHeight="1">
-      <c r="A11" s="19"/>
+      <c r="A11" s="21"/>
       <c r="B11" s="2" t="s">
         <v>11</v>
       </c>
@@ -1211,7 +1215,7 @@
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="19"/>
+      <c r="A12" s="21"/>
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
@@ -1232,7 +1236,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" hidden="1">
-      <c r="A13" s="19"/>
+      <c r="A13" s="21"/>
       <c r="B13" s="2" t="s">
         <v>13</v>
       </c>
@@ -1249,7 +1253,7 @@
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="19"/>
+      <c r="A14" s="21"/>
       <c r="B14" s="2" t="s">
         <v>14</v>
       </c>
@@ -1273,7 +1277,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" hidden="1">
-      <c r="A15" s="19"/>
+      <c r="A15" s="21"/>
       <c r="B15" s="2" t="s">
         <v>15</v>
       </c>
@@ -1292,7 +1296,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" hidden="1">
-      <c r="A16" s="19"/>
+      <c r="A16" s="21"/>
       <c r="B16" s="8" t="s">
         <v>23</v>
       </c>
@@ -1309,7 +1313,7 @@
       </c>
     </row>
     <row r="17" spans="1:7" hidden="1">
-      <c r="A17" s="19"/>
+      <c r="A17" s="21"/>
       <c r="B17" s="8" t="s">
         <v>21</v>
       </c>
@@ -1326,7 +1330,7 @@
       </c>
     </row>
     <row r="18" spans="1:7" hidden="1">
-      <c r="A18" s="19"/>
+      <c r="A18" s="21"/>
       <c r="B18" s="8" t="s">
         <v>22</v>
       </c>
@@ -1343,7 +1347,7 @@
       </c>
     </row>
     <row r="19" spans="1:7" hidden="1">
-      <c r="A19" s="19"/>
+      <c r="A19" s="21"/>
       <c r="B19" s="8" t="s">
         <v>24</v>
       </c>
@@ -1356,7 +1360,7 @@
       </c>
     </row>
     <row r="20" spans="1:7" hidden="1">
-      <c r="A20" s="19"/>
+      <c r="A20" s="21"/>
       <c r="B20" s="11" t="s">
         <v>25</v>
       </c>
@@ -1373,7 +1377,7 @@
       </c>
     </row>
     <row r="21" spans="1:7" hidden="1">
-      <c r="A21" s="19"/>
+      <c r="A21" s="21"/>
       <c r="B21" s="11" t="s">
         <v>27</v>
       </c>
@@ -1388,7 +1392,7 @@
       </c>
     </row>
     <row r="22" spans="1:7" hidden="1">
-      <c r="A22" s="19"/>
+      <c r="A22" s="21"/>
       <c r="B22" s="11"/>
       <c r="C22" s="10"/>
       <c r="D22" s="10"/>

--- a/internal_doc/05.测试设计/自动化/SDV1自动化测试用例分类.xlsx
+++ b/internal_doc/05.测试设计/自动化/SDV1自动化测试用例分类.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="63">
   <si>
     <t>story</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -383,6 +383,14 @@
   </si>
   <si>
     <t>龙阳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>邓强中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴艳</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1083,10 +1091,10 @@
         <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>29</v>

--- a/internal_doc/05.测试设计/自动化/SDV1自动化测试用例分类.xlsx
+++ b/internal_doc/05.测试设计/自动化/SDV1自动化测试用例分类.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="70">
   <si>
     <t>story</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -68,10 +68,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>split</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>sql</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -84,19 +80,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>主子表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>集群管理、节点管理</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>om补充异常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据切分（补充复杂场景）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -171,24 +159,6 @@
     <t>吴艳</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">数据同步：全量同步，正常增量数据同步
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="0" tint="-0.249977111117893"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>数据中心灾备</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>黄晓妮</t>
   </si>
   <si>
@@ -206,6 +176,109 @@
   </si>
   <si>
     <t>次要责任人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基本操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聚集操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>余婷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>低</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OM安装部署、web监控</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄晓妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用例个数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>19个异常用例，不做自动化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不做自动化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>优先基本功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>邓强中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、每个特性由主要责任人和次要责任人共同完成，互相检视代码；主次责任人可以自行商量承担工作量（次要责任人可以承担20%工作量）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2、计划下周二（10月13日）每人抽3到4个用例评审</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安排计划：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>龙阳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴艳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王文净</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴艳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元数据操作：
+domain,
+CS(create,drop,list),
+CL(create,drop,alter,list)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>余婷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄晓妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄晓妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>余婷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4个并发用例，不实现自动化</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -303,22 +376,21 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>基本操作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>聚集操作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>元数据操作：
-domain,
-CS(create,drop,list),
-CL(create,drop,alter,list)</t>
+    <r>
+      <t xml:space="preserve">数据同步：全量同步，正常增量数据同步
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0" tint="-0.249977111117893"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>数据中心灾备</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -326,19 +398,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>低</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OM安装部署、web监控</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄晓妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用例个数</t>
+    <t>主子表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>split</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -346,11 +410,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>19个异常用例，不做自动化</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不做自动化</t>
+    <t>数据切分（补充复杂场景）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -358,39 +418,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>优先基本功能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>邓强中</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4个并发用例，不实现自动化</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、每个特性由主要责任人和次要责任人共同完成，互相检视代码；主次责任人可以自行商量承担工作量（次要责任人可以承担20%工作量）。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2、计划下周二（10月13日）每人抽3到4个用例评审</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>安排计划：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>龙阳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>邓强中</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>吴艳</t>
+    <t>3、计划这周四（10月22日）下午14:00进行第二次用例评审</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -398,7 +426,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -496,6 +524,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -576,7 +612,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -609,80 +645,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -694,7 +663,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CCE8CF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -972,7 +941,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.25" customWidth="1"/>
@@ -992,19 +961,19 @@
       </c>
       <c r="C1" s="19"/>
       <c r="D1" s="18" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E1" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="9" t="s">
         <v>38</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1015,19 +984,19 @@
         <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D2" s="2">
         <v>27</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H2" s="16"/>
     </row>
@@ -1037,22 +1006,22 @@
         <v>4</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D3" s="4">
         <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H3" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="22.5" customHeight="1">
@@ -1061,22 +1030,22 @@
         <v>5</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="D4" s="15">
         <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H4" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="36" customHeight="1">
@@ -1085,41 +1054,41 @@
         <v>6</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D5" s="3">
         <v>8</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>61</v>
+      <c r="E5" s="22" t="s">
+        <v>47</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="13.5" hidden="1" customHeight="1">
       <c r="A6" s="21"/>
       <c r="B6" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="13.5" hidden="1" customHeight="1">
@@ -1132,37 +1101,37 @@
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="25.5" customHeight="1">
       <c r="A8" s="21"/>
       <c r="B8" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="D8" s="3">
         <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H8" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1175,16 +1144,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:8" hidden="1">
@@ -1195,13 +1164,13 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H10" s="16"/>
     </row>
@@ -1213,190 +1182,190 @@
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="21"/>
       <c r="B12" s="2" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>19</v>
+        <v>67</v>
       </c>
       <c r="D12" s="2">
         <v>27</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:8" hidden="1">
       <c r="A13" s="21"/>
       <c r="B13" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="21"/>
       <c r="B14" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="D14" s="6">
         <v>12</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H14" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:8" hidden="1">
       <c r="A15" s="21"/>
       <c r="B15" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:8" hidden="1">
       <c r="A16" s="21"/>
       <c r="B16" s="8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:7" hidden="1">
       <c r="A17" s="21"/>
       <c r="B17" s="8" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:7" hidden="1">
       <c r="A18" s="21"/>
       <c r="B18" s="8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:7" hidden="1">
       <c r="A19" s="21"/>
       <c r="B19" s="8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="14" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:7" hidden="1">
       <c r="A20" s="21"/>
       <c r="B20" s="11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="13" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:7" hidden="1">
       <c r="A21" s="21"/>
       <c r="B21" s="11" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="10"/>
       <c r="E21" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="14" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:7" hidden="1">
@@ -1410,17 +1379,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>58</v>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/05.测试设计/自动化/SDV1自动化测试用例分类.xlsx
+++ b/internal_doc/05.测试设计/自动化/SDV1自动化测试用例分类.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="71">
   <si>
     <t>story</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -419,6 +419,10 @@
   </si>
   <si>
     <t>3、计划这周四（10月22日）下午14:00进行第二次用例评审</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵育</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -639,19 +643,87 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -663,7 +735,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="CCE8CF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -977,7 +1049,7 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1001,7 +1073,7 @@
       <c r="H2" s="16"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="21"/>
+      <c r="A3" s="22"/>
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1012,7 +1084,7 @@
         <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>53</v>
@@ -1025,7 +1097,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="22.5" customHeight="1">
-      <c r="A4" s="21"/>
+      <c r="A4" s="22"/>
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
@@ -1049,7 +1121,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="36" customHeight="1">
-      <c r="A5" s="21"/>
+      <c r="A5" s="22"/>
       <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
@@ -1059,8 +1131,8 @@
       <c r="D5" s="3">
         <v>8</v>
       </c>
-      <c r="E5" s="22" t="s">
-        <v>47</v>
+      <c r="E5" s="20" t="s">
+        <v>70</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>52</v>
@@ -1070,7 +1142,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="13.5" hidden="1" customHeight="1">
-      <c r="A6" s="21"/>
+      <c r="A6" s="22"/>
       <c r="B6" s="5" t="s">
         <v>16</v>
       </c>
@@ -1092,7 +1164,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="13.5" hidden="1" customHeight="1">
-      <c r="A7" s="21"/>
+      <c r="A7" s="22"/>
       <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
@@ -1111,7 +1183,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="25.5" customHeight="1">
-      <c r="A8" s="21"/>
+      <c r="A8" s="22"/>
       <c r="B8" s="2" t="s">
         <v>36</v>
       </c>
@@ -1135,7 +1207,7 @@
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="21"/>
+      <c r="A9" s="22"/>
       <c r="B9" s="2" t="s">
         <v>9</v>
       </c>
@@ -1157,7 +1229,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" hidden="1">
-      <c r="A10" s="21"/>
+      <c r="A10" s="22"/>
       <c r="B10" s="2" t="s">
         <v>10</v>
       </c>
@@ -1175,7 +1247,7 @@
       <c r="H10" s="16"/>
     </row>
     <row r="11" spans="1:8" ht="13.5" hidden="1" customHeight="1">
-      <c r="A11" s="21"/>
+      <c r="A11" s="22"/>
       <c r="B11" s="2" t="s">
         <v>11</v>
       </c>
@@ -1192,7 +1264,7 @@
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="21"/>
+      <c r="A12" s="22"/>
       <c r="B12" s="2" t="s">
         <v>65</v>
       </c>
@@ -1213,7 +1285,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" hidden="1">
-      <c r="A13" s="21"/>
+      <c r="A13" s="22"/>
       <c r="B13" s="2" t="s">
         <v>12</v>
       </c>
@@ -1230,7 +1302,7 @@
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="21"/>
+      <c r="A14" s="22"/>
       <c r="B14" s="2" t="s">
         <v>13</v>
       </c>
@@ -1254,7 +1326,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" hidden="1">
-      <c r="A15" s="21"/>
+      <c r="A15" s="22"/>
       <c r="B15" s="2" t="s">
         <v>14</v>
       </c>
@@ -1273,7 +1345,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" hidden="1">
-      <c r="A16" s="21"/>
+      <c r="A16" s="22"/>
       <c r="B16" s="8" t="s">
         <v>20</v>
       </c>
@@ -1290,7 +1362,7 @@
       </c>
     </row>
     <row r="17" spans="1:7" hidden="1">
-      <c r="A17" s="21"/>
+      <c r="A17" s="22"/>
       <c r="B17" s="8" t="s">
         <v>18</v>
       </c>
@@ -1307,7 +1379,7 @@
       </c>
     </row>
     <row r="18" spans="1:7" hidden="1">
-      <c r="A18" s="21"/>
+      <c r="A18" s="22"/>
       <c r="B18" s="8" t="s">
         <v>19</v>
       </c>
@@ -1324,7 +1396,7 @@
       </c>
     </row>
     <row r="19" spans="1:7" hidden="1">
-      <c r="A19" s="21"/>
+      <c r="A19" s="22"/>
       <c r="B19" s="8" t="s">
         <v>21</v>
       </c>
@@ -1337,7 +1409,7 @@
       </c>
     </row>
     <row r="20" spans="1:7" hidden="1">
-      <c r="A20" s="21"/>
+      <c r="A20" s="22"/>
       <c r="B20" s="11" t="s">
         <v>22</v>
       </c>
@@ -1354,7 +1426,7 @@
       </c>
     </row>
     <row r="21" spans="1:7" hidden="1">
-      <c r="A21" s="21"/>
+      <c r="A21" s="22"/>
       <c r="B21" s="11" t="s">
         <v>24</v>
       </c>
@@ -1369,7 +1441,7 @@
       </c>
     </row>
     <row r="22" spans="1:7" hidden="1">
-      <c r="A22" s="21"/>
+      <c r="A22" s="22"/>
       <c r="B22" s="11"/>
       <c r="C22" s="10"/>
       <c r="D22" s="10"/>
